--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationrange-unitoftime.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationrange-unitoftime.xlsx
@@ -266,7 +266,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 rng-2:存在する場合、低い値は高よりも低い値を持つものとします / If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
   </si>
   <si>
@@ -331,7 +331,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -354,7 +354,7 @@
     <t>低要素が欠落している場合、低境界は不明です。 / If the low element is missing, the low boundary is not known.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -485,7 +485,7 @@
     <t>一部のユニット表現システムのユニットのコンピューター処理可能な形式。 / A computer processable form of the unit in some unit representation system.</t>
   </si>
   <si>
-    <t>優先システムはUCUMですが、スノムCTは（慣習ユニットに）または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+    <t>優先システムはUCUMですが、独自の単位にはSNOMED-CT、または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
   </si>
   <si>
     <t>すべてのフォームに固定されたユニットの計算可能な形式が必要です。UCUMはこれを数量で提供しますが、Snomed CTは多くの関心のある単位を提供します。 / Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
